--- a/artfynd/A 18103-2026 artfynd.xlsx
+++ b/artfynd/A 18103-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129367667</v>
+        <v>129380033</v>
       </c>
       <c r="B2" t="n">
-        <v>100963</v>
+        <v>85534</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>241</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sundberget, Sundberget, Vrm</t>
+          <t>Sund, Sund, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>420109</v>
+        <v>420268</v>
       </c>
       <c r="R2" t="n">
-        <v>6612736</v>
+        <v>6612615</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,45 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129380033</v>
+        <v>129370734</v>
       </c>
       <c r="B3" t="n">
-        <v>85265</v>
+        <v>96338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>241</v>
+        <v>2809</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Shear</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sund, Sund, Vrm</t>
+          <t>Sundberget, Sundberget, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>420268</v>
+        <v>420110</v>
       </c>
       <c r="R3" t="n">
-        <v>6612615</v>
+        <v>6612672</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -866,6 +866,103 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129367667</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sundberget, Sundberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>420109</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6612736</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Forshaga</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nedre Ullerud</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18103-2026 artfynd.xlsx
+++ b/artfynd/A 18103-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129380033</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129370734</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,8 +978,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129367667</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>